--- a/znacilnice.xlsx
+++ b/znacilnice.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\diskFailurePrediction\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBA511B6-61A5-4589-9077-96D536E32458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-83" yWindow="0" windowWidth="11206" windowHeight="13163" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="v faking excel tabelo" sheetId="1" r:id="rId4"/>
+    <sheet name="v faking excel tabelo" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
   <si>
     <t>Stolpec / ID</t>
   </si>
@@ -245,20 +254,69 @@
   </si>
   <si>
     <t>Skupna količina prebranih podatkov.</t>
+  </si>
+  <si>
+    <t>moje dodane značilnice:</t>
+  </si>
+  <si>
+    <t>tip pogona</t>
+  </si>
+  <si>
+    <t>Binarna vrednost (1 za SSD, 0 za HDD). Ključno, ker nekateri parametri (npr. mehanski cikli) za SSD ne obstajajo.</t>
+  </si>
+  <si>
+    <t>jeSSD</t>
+  </si>
+  <si>
+    <t>any_critical_error</t>
+  </si>
+  <si>
+    <t>prisotnost kritične napake</t>
+  </si>
+  <si>
+    <t>Binarna zastavica (1, če je katerikoli od kritičnih parametrov S5, S187, S197 ali S198 večji od 0).</t>
+  </si>
+  <si>
+    <t>total_error_count</t>
+  </si>
+  <si>
+    <t>vsota napak</t>
+  </si>
+  <si>
+    <t>Agregirano število vseh zabeleženih napak na sektorjih. Pokaže splošno stopnjo degradacije diska.</t>
+  </si>
+  <si>
+    <t>error_per_gb</t>
+  </si>
+  <si>
+    <t>napake na gigabyte</t>
+  </si>
+  <si>
+    <t>Razmerje med vsemi napakami in kapaciteto diska. Omogoča pravičnejšo primerjavo med majhnimi in ogromnimi diski.</t>
+  </si>
+  <si>
+    <t>capacity_gigabytes</t>
+  </si>
+  <si>
+    <t>kapaciteta</t>
+  </si>
+  <si>
+    <t>Pretvorba iz bytov da imamo manjša števila.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -269,36 +327,43 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -488,17 +553,24 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:C34"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="23.265625" customWidth="1"/>
+    <col min="2" max="2" width="24.796875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -509,7 +581,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -520,7 +592,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -531,7 +603,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -542,7 +614,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -553,7 +625,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -564,7 +636,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
@@ -575,7 +647,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
@@ -586,7 +658,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>24</v>
       </c>
@@ -597,7 +669,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>27</v>
       </c>
@@ -608,7 +680,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>30</v>
       </c>
@@ -619,7 +691,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>33</v>
       </c>
@@ -630,7 +702,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>36</v>
       </c>
@@ -641,7 +713,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>39</v>
       </c>
@@ -652,7 +724,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>42</v>
       </c>
@@ -663,7 +735,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>45</v>
       </c>
@@ -674,7 +746,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>48</v>
       </c>
@@ -685,7 +757,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>51</v>
       </c>
@@ -696,7 +768,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>54</v>
       </c>
@@ -707,7 +779,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>57</v>
       </c>
@@ -718,7 +790,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>60</v>
       </c>
@@ -729,7 +801,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>63</v>
       </c>
@@ -740,7 +812,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>66</v>
       </c>
@@ -751,7 +823,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>69</v>
       </c>
@@ -762,7 +834,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>72</v>
       </c>
@@ -773,7 +845,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>75</v>
       </c>
@@ -784,7 +856,71 @@
         <v>77</v>
       </c>
     </row>
+    <row r="28" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+    </row>
+    <row r="30" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B30" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B31" t="s">
+        <v>83</v>
+      </c>
+      <c r="C31" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>85</v>
+      </c>
+      <c r="B32" t="s">
+        <v>86</v>
+      </c>
+      <c r="C32" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B33" t="s">
+        <v>89</v>
+      </c>
+      <c r="C33" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>91</v>
+      </c>
+      <c r="B34" t="s">
+        <v>92</v>
+      </c>
+      <c r="C34" t="s">
+        <v>93</v>
+      </c>
+    </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/znacilnice.xlsx
+++ b/znacilnice.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\diskFailurePrediction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBA511B6-61A5-4589-9077-96D536E32458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E44988D9-422F-441C-845F-E06D71E26A68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="11206" windowHeight="13163" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4935" yWindow="3548" windowWidth="16560" windowHeight="9532" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="v faking excel tabelo" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
   <si>
     <t>Stolpec / ID</t>
   </si>
@@ -302,13 +302,19 @@
   </si>
   <si>
     <t>Pretvorba iz bytov da imamo manjša števila.</t>
+  </si>
+  <si>
+    <t>smart_191_raw</t>
+  </si>
+  <si>
+    <t>število napak in težav pri delovanju diska, ki so nastale kot neposredna posledica zunanjih mehanskih tresljajev</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -319,6 +325,22 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -342,9 +364,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -563,364 +587,380 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23.265625" customWidth="1"/>
     <col min="2" max="2" width="24.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:4" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+    </row>
+    <row r="3" spans="1:4" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
+    <row r="4" spans="1:4" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
+    <row r="5" spans="1:4" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
+    <row r="6" spans="1:4" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
+    <row r="7" spans="1:4" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
+    <row r="8" spans="1:4" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
+    <row r="9" spans="1:4" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
+    <row r="10" spans="1:4" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B10" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
+    <row r="11" spans="1:4" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
+    <row r="12" spans="1:4" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C12" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="1" t="s">
+    <row r="13" spans="1:4" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B13" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="1" t="s">
+    <row r="14" spans="1:4" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B14" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C14" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" s="1" t="s">
+    <row r="15" spans="1:4" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B15" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C15" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" s="1" t="s">
+    <row r="16" spans="1:4" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B16" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C16" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="1" t="s">
+    <row r="17" spans="1:3" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B17" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C17" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" s="1" t="s">
+    <row r="18" spans="1:3" ht="12.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B18" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C18" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" s="1" t="s">
+    <row r="19" spans="1:3" ht="12.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B20" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C20" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" s="1" t="s">
+    <row r="21" spans="1:3" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="A21" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B21" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C21" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" s="1" t="s">
+    <row r="22" spans="1:3" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="A22" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B22" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C22" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" s="1" t="s">
+    <row r="23" spans="1:3" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B23" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C23" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" s="1" t="s">
+    <row r="24" spans="1:3" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="A24" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B24" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C24" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" s="1" t="s">
+    <row r="25" spans="1:3" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="A25" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B25" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C25" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" s="1" t="s">
+    <row r="26" spans="1:3" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="A26" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B26" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C26" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" s="1" t="s">
+    <row r="27" spans="1:3" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="A27" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B27" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C27" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="1" t="s">
+    <row r="28" spans="1:3" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B28" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C28" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
     </row>
     <row r="30" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+    </row>
+    <row r="32" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B32" t="s">
         <v>79</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C32" t="s">
         <v>80</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B31" t="s">
-        <v>83</v>
-      </c>
-      <c r="C31" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>85</v>
-      </c>
-      <c r="B32" t="s">
-        <v>86</v>
-      </c>
-      <c r="C32" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B33" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C33" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
+        <v>85</v>
+      </c>
+      <c r="B34" t="s">
+        <v>86</v>
+      </c>
+      <c r="C34" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B35" t="s">
+        <v>89</v>
+      </c>
+      <c r="C35" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
         <v>91</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B36" t="s">
         <v>92</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C36" t="s">
         <v>93</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>